--- a/public/templates/KematianBayi.xlsx
+++ b/public/templates/KematianBayi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44612CE0-4180-493C-BDB0-EDAA7D3103E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517C0ADB-D34F-4E3F-8AEB-6E48D9743F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{27B7D30B-5E07-490C-8CC5-B3823205C0EE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{27B7D30B-5E07-490C-8CC5-B3823205C0EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -656,9 +654,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{036B5577-8E24-44B8-9D0E-D663E403BC6B}">
   <dimension ref="B4:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
@@ -671,15 +669,15 @@
       <c r="G4" s="14"/>
       <c r="H4" s="15"/>
       <c r="I4" s="11">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J4" s="12"/>
       <c r="K4" s="11">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="16"/>
       <c r="D5" s="17"/>
@@ -700,7 +698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -717,7 +715,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="10" t="s">
         <v>5</v>
@@ -732,7 +730,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
       <c r="C8" s="10" t="s">
         <v>6</v>
@@ -747,7 +745,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
       <c r="C9" s="10" t="s">
         <v>7</v>
@@ -762,7 +760,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="10" t="s">
         <v>8</v>
@@ -777,7 +775,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -792,7 +790,7 @@
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="10" t="s">
         <v>10</v>
@@ -807,7 +805,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="10" t="s">
         <v>11</v>
@@ -822,7 +820,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="10" t="s">
         <v>12</v>
@@ -839,11 +837,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C9:H9"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="C14:H14"/>
@@ -852,6 +845,11 @@
     <mergeCell ref="C4:H5"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C13:H13"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
